--- a/dados/excel/folha_mensal.xlsx
+++ b/dados/excel/folha_mensal.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Série temporal" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,22 +127,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -630,7 +630,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -661,17 +661,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Número decimal (#,##0,00)</t>
+          <t>Número inteiro (#,##0)</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -807,7 +807,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>﻿ano</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -845,22 +845,22 @@
       <c r="A2" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="10" t="n">
+      <c r="C2" s="9" t="n">
         <v>70274692.34</v>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="9" t="n">
         <v>46264773.18</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="10" t="n">
         <v>16228</v>
       </c>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="10" t="n">
         <v>11290</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="9" t="n">
         <v>6224.51</v>
       </c>
     </row>
@@ -868,22 +868,22 @@
       <c r="A3" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="12" t="n">
         <v>59377915.16</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="12" t="n">
         <v>37994401.04</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="13" t="n">
         <v>10492</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="13" t="n">
         <v>9729</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="12" t="n">
         <v>6103.19</v>
       </c>
     </row>
@@ -891,22 +891,22 @@
       <c r="A4" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B4" s="9" t="n">
+      <c r="B4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="10" t="n">
+      <c r="C4" s="9" t="n">
         <v>68865322.84</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="9" t="n">
         <v>46572057.23</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="10" t="n">
         <v>12237</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="10" t="n">
         <v>11337</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="9" t="n">
         <v>6074.39</v>
       </c>
     </row>
@@ -914,22 +914,22 @@
       <c r="A5" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="12" t="n">
         <v>72460130.02</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="12" t="n">
         <v>46841409.07</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="13" t="n">
         <v>12387</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="13" t="n">
         <v>11579</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="12" t="n">
         <v>6257.89</v>
       </c>
     </row>
@@ -937,22 +937,22 @@
       <c r="A6" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="10" t="n">
+      <c r="C6" s="9" t="n">
         <v>75198274.98</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>49309387.96</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="10" t="n">
         <v>12490</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="10" t="n">
         <v>11767</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="9" t="n">
         <v>6390.61</v>
       </c>
     </row>
@@ -960,22 +960,22 @@
       <c r="A7" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <v>74859337.17</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>49004300.26</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>12715</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>11915</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <v>6282.78</v>
       </c>
     </row>
@@ -983,22 +983,22 @@
       <c r="A8" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="9" t="n">
         <v>75946079.45</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>50422881.3</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="10" t="n">
         <v>12832</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="10" t="n">
         <v>11793</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="9" t="n">
         <v>6439.93</v>
       </c>
     </row>
@@ -1006,22 +1006,22 @@
       <c r="A9" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="12" t="n">
         <v>73121820.31999999</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="12" t="n">
         <v>47634513.74</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="13" t="n">
         <v>12420</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="13" t="n">
         <v>11836</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="12" t="n">
         <v>6177.92</v>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       <c r="A10" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="9" t="n">
         <v>75871210.59</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>49848950.19</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="10" t="n">
         <v>13247</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="F10" s="10" t="n">
         <v>12028</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="9" t="n">
         <v>6307.88</v>
       </c>
     </row>
@@ -1052,22 +1052,22 @@
       <c r="A11" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <v>78465962.79000001</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="12" t="n">
         <v>50698175.01</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="13" t="n">
         <v>14124</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="13" t="n">
         <v>11945</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="12" t="n">
         <v>6568.94</v>
       </c>
     </row>
@@ -1075,22 +1075,22 @@
       <c r="A12" s="8" t="n">
         <v>2022</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="9" t="n">
         <v>103275264.46</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>76327895.08</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="10" t="n">
         <v>12523</v>
       </c>
-      <c r="F12" s="8" t="n">
+      <c r="F12" s="10" t="n">
         <v>11898</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="9" t="n">
         <v>8680.049999999999</v>
       </c>
     </row>
@@ -1098,22 +1098,22 @@
       <c r="A13" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C13" s="13" t="n">
+      <c r="C13" s="12" t="n">
         <v>141153690.4</v>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="12" t="n">
         <v>68649575.25</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="13" t="n">
         <v>22028</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="13" t="n">
         <v>11712</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="G13" s="12" t="n">
         <v>12052.06</v>
       </c>
     </row>
@@ -1121,22 +1121,22 @@
       <c r="A14" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B14" s="9" t="n">
+      <c r="B14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="9" t="n">
         <v>81143980.59</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>53655512.03</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="10" t="n">
         <v>15477</v>
       </c>
-      <c r="F14" s="8" t="n">
+      <c r="F14" s="10" t="n">
         <v>11022</v>
       </c>
-      <c r="G14" s="10" t="n">
+      <c r="G14" s="9" t="n">
         <v>7362</v>
       </c>
     </row>
@@ -1144,22 +1144,22 @@
       <c r="A15" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B15" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="12" t="n">
         <v>83152573.62</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="12" t="n">
         <v>52842860.7</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="13" t="n">
         <v>11158</v>
       </c>
-      <c r="F15" s="11" t="n">
+      <c r="F15" s="13" t="n">
         <v>10205</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="12" t="n">
         <v>8148.22</v>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       <c r="A16" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B16" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C16" s="10" t="n">
+      <c r="C16" s="9" t="n">
         <v>91939165.01000001</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>60869810.95</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="10" t="n">
         <v>12767</v>
       </c>
-      <c r="F16" s="8" t="n">
+      <c r="F16" s="10" t="n">
         <v>11758</v>
       </c>
-      <c r="G16" s="10" t="n">
+      <c r="G16" s="9" t="n">
         <v>7819.29</v>
       </c>
     </row>
@@ -1190,22 +1190,22 @@
       <c r="A17" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="12" t="n">
         <v>80393809.94</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="12" t="n">
         <v>52004426.64</v>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="13" t="n">
         <v>17732</v>
       </c>
-      <c r="F17" s="11" t="n">
+      <c r="F17" s="13" t="n">
         <v>12416</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="G17" s="12" t="n">
         <v>6475.02</v>
       </c>
     </row>
@@ -1213,22 +1213,22 @@
       <c r="A18" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B18" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C18" s="10" t="n">
+      <c r="C18" s="9" t="n">
         <v>80588758.53</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>52252740.97</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="10" t="n">
         <v>13257</v>
       </c>
-      <c r="F18" s="8" t="n">
+      <c r="F18" s="10" t="n">
         <v>12458</v>
       </c>
-      <c r="G18" s="10" t="n">
+      <c r="G18" s="9" t="n">
         <v>6468.84</v>
       </c>
     </row>
@@ -1236,22 +1236,22 @@
       <c r="A19" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <v>83834223.13</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <v>54598332.06</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="13" t="n">
         <v>13368</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="13" t="n">
         <v>12705</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <v>6598.52</v>
       </c>
     </row>
@@ -1259,22 +1259,22 @@
       <c r="A20" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B20" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="9" t="n">
         <v>87293434.09</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>57405219.03</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="10" t="n">
         <v>13679</v>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F20" s="10" t="n">
         <v>12540</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G20" s="9" t="n">
         <v>6961.2</v>
       </c>
     </row>
@@ -1282,22 +1282,22 @@
       <c r="A21" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="13" t="n">
+      <c r="C21" s="12" t="n">
         <v>89727793.84999999</v>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="12" t="n">
         <v>59700843.05</v>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="13" t="n">
         <v>13391</v>
       </c>
-      <c r="F21" s="11" t="n">
+      <c r="F21" s="13" t="n">
         <v>12448</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="G21" s="12" t="n">
         <v>7208.21</v>
       </c>
     </row>
@@ -1305,22 +1305,22 @@
       <c r="A22" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B22" s="9" t="n">
+      <c r="B22" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C22" s="10" t="n">
+      <c r="C22" s="9" t="n">
         <v>89621692.59</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>59321469.37</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="10" t="n">
         <v>13503</v>
       </c>
-      <c r="F22" s="8" t="n">
+      <c r="F22" s="10" t="n">
         <v>12667</v>
       </c>
-      <c r="G22" s="10" t="n">
+      <c r="G22" s="9" t="n">
         <v>7075.21</v>
       </c>
     </row>
@@ -1328,22 +1328,22 @@
       <c r="A23" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B23" s="12" t="n">
+      <c r="B23" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C23" s="13" t="n">
+      <c r="C23" s="12" t="n">
         <v>89485511.73999999</v>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="12" t="n">
         <v>59514997.75</v>
       </c>
-      <c r="E23" s="11" t="n">
+      <c r="E23" s="13" t="n">
         <v>13297</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="13" t="n">
         <v>12629</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>7085.72</v>
       </c>
     </row>
@@ -1351,22 +1351,22 @@
       <c r="A24" s="8" t="n">
         <v>2023</v>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B24" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="9" t="n">
         <v>120240059.83</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>90035744.19</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="10" t="n">
         <v>13613</v>
       </c>
-      <c r="F24" s="8" t="n">
+      <c r="F24" s="10" t="n">
         <v>12685</v>
       </c>
-      <c r="G24" s="10" t="n">
+      <c r="G24" s="9" t="n">
         <v>9478.92</v>
       </c>
     </row>
@@ -1374,22 +1374,22 @@
       <c r="A25" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="B25" s="12" t="n">
+      <c r="B25" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="12" t="n">
         <v>169348904.26</v>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="12" t="n">
         <v>83114048.08</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="13" t="n">
         <v>32742</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="13" t="n">
         <v>12591</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G25" s="12" t="n">
         <v>13450</v>
       </c>
     </row>
@@ -1397,22 +1397,22 @@
       <c r="A26" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C26" s="10" t="n">
+      <c r="C26" s="9" t="n">
         <v>96436581.84999999</v>
       </c>
-      <c r="D26" s="10" t="n">
+      <c r="D26" s="9" t="n">
         <v>64379607.65</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="10" t="n">
         <v>16598</v>
       </c>
-      <c r="F26" s="8" t="n">
+      <c r="F26" s="10" t="n">
         <v>11873</v>
       </c>
-      <c r="G26" s="10" t="n">
+      <c r="G26" s="9" t="n">
         <v>8122.34</v>
       </c>
     </row>
@@ -1420,22 +1420,22 @@
       <c r="A27" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B27" s="12" t="n">
+      <c r="B27" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C27" s="13" t="n">
+      <c r="C27" s="12" t="n">
         <v>87603467.53</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="12" t="n">
         <v>57867232.99</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="13" t="n">
         <v>11719</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="13" t="n">
         <v>10977</v>
       </c>
-      <c r="G27" s="13" t="n">
+      <c r="G27" s="12" t="n">
         <v>7980.64</v>
       </c>
     </row>
@@ -1443,22 +1443,22 @@
       <c r="A28" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C28" s="9" t="n">
         <v>109326020.21</v>
       </c>
-      <c r="D28" s="10" t="n">
+      <c r="D28" s="9" t="n">
         <v>74621187.86</v>
       </c>
-      <c r="E28" s="8" t="n">
+      <c r="E28" s="10" t="n">
         <v>13082</v>
       </c>
-      <c r="F28" s="8" t="n">
+      <c r="F28" s="10" t="n">
         <v>12357</v>
       </c>
-      <c r="G28" s="10" t="n">
+      <c r="G28" s="9" t="n">
         <v>8847.290000000001</v>
       </c>
     </row>
@@ -1466,22 +1466,22 @@
       <c r="A29" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B29" s="12" t="n">
+      <c r="B29" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="13" t="n">
+      <c r="C29" s="12" t="n">
         <v>101013090.35</v>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="12" t="n">
         <v>68866234.92</v>
       </c>
-      <c r="E29" s="11" t="n">
+      <c r="E29" s="13" t="n">
         <v>14050</v>
       </c>
-      <c r="F29" s="11" t="n">
+      <c r="F29" s="13" t="n">
         <v>13010</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="G29" s="12" t="n">
         <v>7764.27</v>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       <c r="A30" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C30" s="10" t="n">
+      <c r="C30" s="9" t="n">
         <v>98870785.13</v>
       </c>
-      <c r="D30" s="10" t="n">
+      <c r="D30" s="9" t="n">
         <v>66265565.21</v>
       </c>
-      <c r="E30" s="8" t="n">
+      <c r="E30" s="10" t="n">
         <v>13914</v>
       </c>
-      <c r="F30" s="8" t="n">
+      <c r="F30" s="10" t="n">
         <v>13116</v>
       </c>
-      <c r="G30" s="10" t="n">
+      <c r="G30" s="9" t="n">
         <v>7538.18</v>
       </c>
     </row>
@@ -1512,22 +1512,22 @@
       <c r="A31" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B31" s="12" t="n">
+      <c r="B31" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C31" s="13" t="n">
+      <c r="C31" s="12" t="n">
         <v>97820809.59999999</v>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="12" t="n">
         <v>65706895.71</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="13" t="n">
         <v>13878</v>
       </c>
-      <c r="F31" s="11" t="n">
+      <c r="F31" s="13" t="n">
         <v>13140</v>
       </c>
-      <c r="G31" s="13" t="n">
+      <c r="G31" s="12" t="n">
         <v>7444.51</v>
       </c>
     </row>
@@ -1535,22 +1535,22 @@
       <c r="A32" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B32" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="9" t="n">
         <v>99864776.48</v>
       </c>
-      <c r="D32" s="10" t="n">
+      <c r="D32" s="9" t="n">
         <v>67550639.78</v>
       </c>
-      <c r="E32" s="8" t="n">
+      <c r="E32" s="10" t="n">
         <v>14801</v>
       </c>
-      <c r="F32" s="8" t="n">
+      <c r="F32" s="10" t="n">
         <v>13146</v>
       </c>
-      <c r="G32" s="10" t="n">
+      <c r="G32" s="9" t="n">
         <v>7596.59</v>
       </c>
     </row>
@@ -1558,22 +1558,22 @@
       <c r="A33" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="12" t="n">
         <v>95317817.08</v>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="12" t="n">
         <v>63470729.39</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="13" t="n">
         <v>13722</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="13" t="n">
         <v>12776</v>
       </c>
-      <c r="G33" s="13" t="n">
+      <c r="G33" s="12" t="n">
         <v>7460.69</v>
       </c>
     </row>
@@ -1581,22 +1581,22 @@
       <c r="A34" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B34" s="9" t="n">
+      <c r="B34" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C34" s="10" t="n">
+      <c r="C34" s="9" t="n">
         <v>97837400.11</v>
       </c>
-      <c r="D34" s="10" t="n">
+      <c r="D34" s="9" t="n">
         <v>65645415.39</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="10" t="n">
         <v>14038</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F34" s="10" t="n">
         <v>13209</v>
       </c>
-      <c r="G34" s="10" t="n">
+      <c r="G34" s="9" t="n">
         <v>7406.87</v>
       </c>
     </row>
@@ -1604,22 +1604,22 @@
       <c r="A35" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B35" s="12" t="n">
+      <c r="B35" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="12" t="n">
         <v>98516206.09999999</v>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="12" t="n">
         <v>65803003.71</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="13" t="n">
         <v>13993</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="13" t="n">
         <v>13288</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="G35" s="12" t="n">
         <v>7413.92</v>
       </c>
     </row>
@@ -1627,22 +1627,22 @@
       <c r="A36" s="8" t="n">
         <v>2024</v>
       </c>
-      <c r="B36" s="9" t="n">
+      <c r="B36" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C36" s="10" t="n">
+      <c r="C36" s="9" t="n">
         <v>164842333.46</v>
       </c>
-      <c r="D36" s="10" t="n">
+      <c r="D36" s="9" t="n">
         <v>98718219.59</v>
       </c>
-      <c r="E36" s="8" t="n">
+      <c r="E36" s="10" t="n">
         <v>23707</v>
       </c>
-      <c r="F36" s="8" t="n">
+      <c r="F36" s="10" t="n">
         <v>13157</v>
       </c>
-      <c r="G36" s="10" t="n">
+      <c r="G36" s="9" t="n">
         <v>12528.87</v>
       </c>
     </row>
@@ -1650,22 +1650,22 @@
       <c r="A37" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="B37" s="12" t="n">
+      <c r="B37" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="12" t="n">
         <v>174687312.44</v>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="12" t="n">
         <v>85068631.7</v>
       </c>
-      <c r="E37" s="11" t="n">
+      <c r="E37" s="13" t="n">
         <v>24044</v>
       </c>
-      <c r="F37" s="11" t="n">
+      <c r="F37" s="13" t="n">
         <v>13051</v>
       </c>
-      <c r="G37" s="13" t="n">
+      <c r="G37" s="12" t="n">
         <v>13384.98</v>
       </c>
     </row>
@@ -1673,22 +1673,22 @@
       <c r="A38" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B38" s="9" t="n">
+      <c r="B38" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C38" s="10" t="n">
+      <c r="C38" s="9" t="n">
         <v>104916189.43</v>
       </c>
-      <c r="D38" s="10" t="n">
+      <c r="D38" s="9" t="n">
         <v>70457665.55</v>
       </c>
-      <c r="E38" s="8" t="n">
+      <c r="E38" s="10" t="n">
         <v>17395</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="10" t="n">
         <v>12482</v>
       </c>
-      <c r="G38" s="10" t="n">
+      <c r="G38" s="9" t="n">
         <v>8405.4</v>
       </c>
     </row>
@@ -1696,22 +1696,22 @@
       <c r="A39" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B39" s="12" t="n">
+      <c r="B39" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="12" t="n">
         <v>97394039.81999999</v>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="12" t="n">
         <v>63839757.73</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="13" t="n">
         <v>11839</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="13" t="n">
         <v>11070</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G39" s="12" t="n">
         <v>8798.02</v>
       </c>
     </row>
@@ -1719,22 +1719,22 @@
       <c r="A40" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B40" s="9" t="n">
+      <c r="B40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C40" s="10" t="n">
+      <c r="C40" s="9" t="n">
         <v>122414115.01</v>
       </c>
-      <c r="D40" s="10" t="n">
+      <c r="D40" s="9" t="n">
         <v>80340768.22</v>
       </c>
-      <c r="E40" s="8" t="n">
+      <c r="E40" s="10" t="n">
         <v>23921</v>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="10" t="n">
         <v>13420</v>
       </c>
-      <c r="G40" s="10" t="n">
+      <c r="G40" s="9" t="n">
         <v>9121.77</v>
       </c>
     </row>
@@ -1742,22 +1742,22 @@
       <c r="A41" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B41" s="12" t="n">
+      <c r="B41" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C41" s="13" t="n">
+      <c r="C41" s="12" t="n">
         <v>107027107.06</v>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="12" t="n">
         <v>70517149.54000001</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="13" t="n">
         <v>14036</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="13" t="n">
         <v>13048</v>
       </c>
-      <c r="G41" s="13" t="n">
+      <c r="G41" s="12" t="n">
         <v>8202.57</v>
       </c>
     </row>
@@ -1765,22 +1765,22 @@
       <c r="A42" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B42" s="9" t="n">
+      <c r="B42" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C42" s="10" t="n">
+      <c r="C42" s="9" t="n">
         <v>108027237.48</v>
       </c>
-      <c r="D42" s="10" t="n">
+      <c r="D42" s="9" t="n">
         <v>71358533.19</v>
       </c>
-      <c r="E42" s="8" t="n">
+      <c r="E42" s="10" t="n">
         <v>14379</v>
       </c>
-      <c r="F42" s="8" t="n">
+      <c r="F42" s="10" t="n">
         <v>13251</v>
       </c>
-      <c r="G42" s="10" t="n">
+      <c r="G42" s="9" t="n">
         <v>8152.38</v>
       </c>
     </row>
@@ -1788,22 +1788,22 @@
       <c r="A43" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B43" s="12" t="n">
+      <c r="B43" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="12" t="n">
         <v>112514239.75</v>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="12" t="n">
         <v>73576791.7</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="13" t="n">
         <v>14272</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="13" t="n">
         <v>13371</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="G43" s="12" t="n">
         <v>8414.799999999999</v>
       </c>
     </row>
@@ -1811,22 +1811,22 @@
       <c r="A44" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B44" s="9" t="n">
+      <c r="B44" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C44" s="10" t="n">
+      <c r="C44" s="9" t="n">
         <v>112522782.32</v>
       </c>
-      <c r="D44" s="10" t="n">
+      <c r="D44" s="9" t="n">
         <v>74670792.98</v>
       </c>
-      <c r="E44" s="8" t="n">
+      <c r="E44" s="10" t="n">
         <v>14822</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="10" t="n">
         <v>13405</v>
       </c>
-      <c r="G44" s="10" t="n">
+      <c r="G44" s="9" t="n">
         <v>8394.09</v>
       </c>
     </row>
@@ -1834,22 +1834,22 @@
       <c r="A45" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B45" s="12" t="n">
+      <c r="B45" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C45" s="13" t="n">
+      <c r="C45" s="12" t="n">
         <v>110463399.24</v>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="12" t="n">
         <v>72605047.03</v>
       </c>
-      <c r="E45" s="11" t="n">
+      <c r="E45" s="13" t="n">
         <v>13881</v>
       </c>
-      <c r="F45" s="11" t="n">
+      <c r="F45" s="13" t="n">
         <v>13062</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="G45" s="12" t="n">
         <v>8456.85</v>
       </c>
     </row>
@@ -1857,22 +1857,22 @@
       <c r="A46" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B46" s="9" t="n">
+      <c r="B46" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="C46" s="10" t="n">
+      <c r="C46" s="9" t="n">
         <v>111734035.32</v>
       </c>
-      <c r="D46" s="10" t="n">
+      <c r="D46" s="9" t="n">
         <v>73720801.06</v>
       </c>
-      <c r="E46" s="8" t="n">
+      <c r="E46" s="10" t="n">
         <v>14691</v>
       </c>
-      <c r="F46" s="8" t="n">
+      <c r="F46" s="10" t="n">
         <v>13540</v>
       </c>
-      <c r="G46" s="10" t="n">
+      <c r="G46" s="9" t="n">
         <v>8252.139999999999</v>
       </c>
     </row>
@@ -1880,22 +1880,22 @@
       <c r="A47" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B47" s="12" t="n">
+      <c r="B47" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C47" s="13" t="n">
+      <c r="C47" s="12" t="n">
         <v>110279554.48</v>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="12" t="n">
         <v>72167021.81999999</v>
       </c>
-      <c r="E47" s="11" t="n">
+      <c r="E47" s="13" t="n">
         <v>14463</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F47" s="13" t="n">
         <v>13654</v>
       </c>
-      <c r="G47" s="13" t="n">
+      <c r="G47" s="12" t="n">
         <v>8076.72</v>
       </c>
     </row>
@@ -1903,22 +1903,22 @@
       <c r="A48" s="8" t="n">
         <v>2025</v>
       </c>
-      <c r="B48" s="9" t="n">
+      <c r="B48" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="C48" s="10" t="n">
+      <c r="C48" s="9" t="n">
         <v>147355080.14</v>
       </c>
-      <c r="D48" s="10" t="n">
+      <c r="D48" s="9" t="n">
         <v>109047799.11</v>
       </c>
-      <c r="E48" s="8" t="n">
+      <c r="E48" s="10" t="n">
         <v>14488</v>
       </c>
-      <c r="F48" s="8" t="n">
+      <c r="F48" s="10" t="n">
         <v>13546</v>
       </c>
-      <c r="G48" s="10" t="n">
+      <c r="G48" s="9" t="n">
         <v>10878.12</v>
       </c>
     </row>
@@ -1926,22 +1926,22 @@
       <c r="A49" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="B49" s="12" t="n">
+      <c r="B49" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C49" s="13" t="n">
+      <c r="C49" s="12" t="n">
         <v>195618641.99</v>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="12" t="n">
         <v>97058280.88</v>
       </c>
-      <c r="E49" s="11" t="n">
+      <c r="E49" s="13" t="n">
         <v>24626</v>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F49" s="13" t="n">
         <v>13474</v>
       </c>
-      <c r="G49" s="13" t="n">
+      <c r="G49" s="12" t="n">
         <v>14518.23</v>
       </c>
     </row>
@@ -1949,22 +1949,22 @@
       <c r="A50" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B50" s="9" t="n">
+      <c r="B50" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="9" t="n">
         <v>119601635.45</v>
       </c>
-      <c r="D50" s="10" t="n">
+      <c r="D50" s="9" t="n">
         <v>81010131.39</v>
       </c>
-      <c r="E50" s="8" t="n">
+      <c r="E50" s="10" t="n">
         <v>17943</v>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="10" t="n">
         <v>12928</v>
       </c>
-      <c r="G50" s="10" t="n">
+      <c r="G50" s="9" t="n">
         <v>9251.360000000001</v>
       </c>
     </row>
@@ -1972,22 +1972,22 @@
       <c r="A51" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B51" s="12" t="n">
+      <c r="B51" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="13" t="n">
+      <c r="C51" s="12" t="n">
         <v>103607784.27</v>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="12" t="n">
         <v>68164494.37</v>
       </c>
-      <c r="E51" s="11" t="n">
+      <c r="E51" s="13" t="n">
         <v>11850</v>
       </c>
-      <c r="F51" s="11" t="n">
+      <c r="F51" s="13" t="n">
         <v>10900</v>
       </c>
-      <c r="G51" s="13" t="n">
+      <c r="G51" s="12" t="n">
         <v>9505.299999999999</v>
       </c>
     </row>
@@ -1995,22 +1995,22 @@
       <c r="A52" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B52" s="9" t="n">
+      <c r="B52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="C52" s="10" t="n">
+      <c r="C52" s="9" t="n">
         <v>130341240.2</v>
       </c>
-      <c r="D52" s="10" t="n">
+      <c r="D52" s="9" t="n">
         <v>88526022.09</v>
       </c>
-      <c r="E52" s="8" t="n">
+      <c r="E52" s="10" t="n">
         <v>14490</v>
       </c>
-      <c r="F52" s="8" t="n">
+      <c r="F52" s="10" t="n">
         <v>13568</v>
       </c>
-      <c r="G52" s="10" t="n">
+      <c r="G52" s="9" t="n">
         <v>9606.52</v>
       </c>
     </row>
@@ -2018,22 +2018,22 @@
       <c r="A53" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B53" s="12" t="n">
+      <c r="B53" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C53" s="13" t="n">
+      <c r="C53" s="12" t="n">
         <v>117938726.44</v>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="12" t="n">
         <v>78406136.02</v>
       </c>
-      <c r="E53" s="11" t="n">
+      <c r="E53" s="13" t="n">
         <v>14674</v>
       </c>
-      <c r="F53" s="11" t="n">
+      <c r="F53" s="13" t="n">
         <v>13660</v>
       </c>
-      <c r="G53" s="13" t="n">
+      <c r="G53" s="12" t="n">
         <v>8633.870000000001</v>
       </c>
     </row>
@@ -2041,22 +2041,22 @@
       <c r="A54" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B54" s="9" t="n">
+      <c r="B54" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="9" t="n">
         <v>120069417.43</v>
       </c>
-      <c r="D54" s="10" t="n">
+      <c r="D54" s="9" t="n">
         <v>78977353.33</v>
       </c>
-      <c r="E54" s="8" t="n">
+      <c r="E54" s="10" t="n">
         <v>14684</v>
       </c>
-      <c r="F54" s="8" t="n">
+      <c r="F54" s="10" t="n">
         <v>13568</v>
       </c>
-      <c r="G54" s="10" t="n">
+      <c r="G54" s="9" t="n">
         <v>8849.459999999999</v>
       </c>
     </row>
@@ -2064,22 +2064,22 @@
       <c r="A55" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B55" s="12" t="n">
+      <c r="B55" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C55" s="13" t="n">
+      <c r="C55" s="12" t="n">
         <v>123384176.69</v>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="12" t="n">
         <v>81026085.91</v>
       </c>
-      <c r="E55" s="11" t="n">
+      <c r="E55" s="13" t="n">
         <v>14761</v>
       </c>
-      <c r="F55" s="11" t="n">
+      <c r="F55" s="13" t="n">
         <v>13851</v>
       </c>
-      <c r="G55" s="13" t="n">
+      <c r="G55" s="12" t="n">
         <v>8907.959999999999</v>
       </c>
     </row>
@@ -2087,22 +2087,22 @@
       <c r="A56" s="8" t="n">
         <v>2026</v>
       </c>
-      <c r="B56" s="9" t="n">
+      <c r="B56" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="C56" s="10" t="n">
+      <c r="C56" s="9" t="n">
         <v>138886330.38</v>
       </c>
-      <c r="D56" s="10" t="n">
+      <c r="D56" s="9" t="n">
         <v>87440138.01000001</v>
       </c>
-      <c r="E56" s="8" t="n">
+      <c r="E56" s="10" t="n">
         <v>19364</v>
       </c>
-      <c r="F56" s="8" t="n">
+      <c r="F56" s="10" t="n">
         <v>13898</v>
       </c>
-      <c r="G56" s="10" t="n">
+      <c r="G56" s="9" t="n">
         <v>9993.26</v>
       </c>
     </row>
@@ -2110,27 +2110,50 @@
       <c r="A57" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="B57" s="12" t="n">
+      <c r="B57" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="C57" s="13" t="n">
+      <c r="C57" s="12" t="n">
         <v>124784562.77</v>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="12" t="n">
         <v>81674509.95</v>
       </c>
-      <c r="E57" s="11" t="n">
+      <c r="E57" s="13" t="n">
         <v>14685</v>
       </c>
-      <c r="F57" s="11" t="n">
+      <c r="F57" s="13" t="n">
         <v>13916</v>
       </c>
-      <c r="G57" s="13" t="n">
+      <c r="G57" s="12" t="n">
         <v>8966.98</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <v>129971219.82</v>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>86079101.33</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>15255</v>
+      </c>
+      <c r="F58" s="10" t="n">
+        <v>14469</v>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>8982.74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G57"/>
+  <autoFilter ref="A1:G58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2141,7 +2164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B59"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2170,7 +2193,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1/2022</t>
         </is>
       </c>
       <c r="B4" s="15" t="n">
@@ -2180,7 +2203,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2/2022</t>
         </is>
       </c>
       <c r="B5" s="15" t="n">
@@ -2190,7 +2213,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>3/2022</t>
         </is>
       </c>
       <c r="B6" s="15" t="n">
@@ -2200,7 +2223,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>4/2022</t>
         </is>
       </c>
       <c r="B7" s="15" t="n">
@@ -2210,7 +2233,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>5/2022</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
@@ -2220,7 +2243,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>6/2022</t>
         </is>
       </c>
       <c r="B9" s="15" t="n">
@@ -2230,7 +2253,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>7/2022</t>
         </is>
       </c>
       <c r="B10" s="15" t="n">
@@ -2240,7 +2263,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>8/2022</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
@@ -2250,7 +2273,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>9/2022</t>
         </is>
       </c>
       <c r="B12" s="15" t="n">
@@ -2260,7 +2283,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>10/2022</t>
         </is>
       </c>
       <c r="B13" s="15" t="n">
@@ -2270,7 +2293,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>11/2022</t>
         </is>
       </c>
       <c r="B14" s="15" t="n">
@@ -2280,7 +2303,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="B15" s="15" t="n">
@@ -2290,7 +2313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1/2023</t>
         </is>
       </c>
       <c r="B16" s="15" t="n">
@@ -2300,7 +2323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2/2023</t>
         </is>
       </c>
       <c r="B17" s="15" t="n">
@@ -2310,7 +2333,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>3/2023</t>
         </is>
       </c>
       <c r="B18" s="15" t="n">
@@ -2320,7 +2343,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>4/2023</t>
         </is>
       </c>
       <c r="B19" s="15" t="n">
@@ -2330,7 +2353,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>5/2023</t>
         </is>
       </c>
       <c r="B20" s="15" t="n">
@@ -2340,7 +2363,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>6/2023</t>
         </is>
       </c>
       <c r="B21" s="15" t="n">
@@ -2350,7 +2373,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>7/2023</t>
         </is>
       </c>
       <c r="B22" s="15" t="n">
@@ -2360,7 +2383,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>8/2023</t>
         </is>
       </c>
       <c r="B23" s="15" t="n">
@@ -2370,7 +2393,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>9/2023</t>
         </is>
       </c>
       <c r="B24" s="15" t="n">
@@ -2380,7 +2403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>10/2023</t>
         </is>
       </c>
       <c r="B25" s="15" t="n">
@@ -2390,7 +2413,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>11/2023</t>
         </is>
       </c>
       <c r="B26" s="15" t="n">
@@ -2400,7 +2423,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="B27" s="15" t="n">
@@ -2410,7 +2433,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1/2024</t>
         </is>
       </c>
       <c r="B28" s="15" t="n">
@@ -2420,7 +2443,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2/2024</t>
         </is>
       </c>
       <c r="B29" s="15" t="n">
@@ -2430,7 +2453,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>3/2024</t>
         </is>
       </c>
       <c r="B30" s="15" t="n">
@@ -2440,7 +2463,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>4/2024</t>
         </is>
       </c>
       <c r="B31" s="15" t="n">
@@ -2450,7 +2473,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>5/2024</t>
         </is>
       </c>
       <c r="B32" s="15" t="n">
@@ -2460,7 +2483,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>6/2024</t>
         </is>
       </c>
       <c r="B33" s="15" t="n">
@@ -2470,7 +2493,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>7/2024</t>
         </is>
       </c>
       <c r="B34" s="15" t="n">
@@ -2480,7 +2503,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>8/2024</t>
         </is>
       </c>
       <c r="B35" s="15" t="n">
@@ -2490,7 +2513,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>9/2024</t>
         </is>
       </c>
       <c r="B36" s="15" t="n">
@@ -2500,7 +2523,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>10/2024</t>
         </is>
       </c>
       <c r="B37" s="15" t="n">
@@ -2510,7 +2533,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>11/2024</t>
         </is>
       </c>
       <c r="B38" s="15" t="n">
@@ -2520,7 +2543,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>12/2024</t>
         </is>
       </c>
       <c r="B39" s="15" t="n">
@@ -2530,7 +2553,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>1/2025</t>
         </is>
       </c>
       <c r="B40" s="15" t="n">
@@ -2540,7 +2563,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2/2025</t>
         </is>
       </c>
       <c r="B41" s="15" t="n">
@@ -2550,7 +2573,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>3/2025</t>
         </is>
       </c>
       <c r="B42" s="15" t="n">
@@ -2560,7 +2583,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>4/2025</t>
         </is>
       </c>
       <c r="B43" s="15" t="n">
@@ -2570,7 +2593,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>5/2025</t>
         </is>
       </c>
       <c r="B44" s="15" t="n">
@@ -2580,7 +2603,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>6/2025</t>
         </is>
       </c>
       <c r="B45" s="15" t="n">
@@ -2590,7 +2613,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>7/2025</t>
         </is>
       </c>
       <c r="B46" s="15" t="n">
@@ -2600,7 +2623,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>8/2025</t>
         </is>
       </c>
       <c r="B47" s="15" t="n">
@@ -2610,7 +2633,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>9/2025</t>
         </is>
       </c>
       <c r="B48" s="15" t="n">
@@ -2620,7 +2643,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="B49" s="15" t="n">
@@ -2630,7 +2653,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>11/2025</t>
         </is>
       </c>
       <c r="B50" s="15" t="n">
@@ -2640,7 +2663,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>12/2025</t>
         </is>
       </c>
       <c r="B51" s="15" t="n">
@@ -2650,7 +2673,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1/2026</t>
         </is>
       </c>
       <c r="B52" s="15" t="n">
@@ -2660,7 +2683,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2/2026</t>
         </is>
       </c>
       <c r="B53" s="15" t="n">
@@ -2670,7 +2693,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>3/2026</t>
         </is>
       </c>
       <c r="B54" s="15" t="n">
@@ -2680,7 +2703,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>4/2026</t>
         </is>
       </c>
       <c r="B55" s="15" t="n">
@@ -2690,7 +2713,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>5/2026</t>
         </is>
       </c>
       <c r="B56" s="15" t="n">
@@ -2700,7 +2723,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>6/2026</t>
         </is>
       </c>
       <c r="B57" s="15" t="n">
@@ -2710,7 +2733,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>7/2026</t>
         </is>
       </c>
       <c r="B58" s="15" t="n">
@@ -2720,11 +2743,21 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>8/2026</t>
         </is>
       </c>
       <c r="B59" s="15" t="n">
         <v>124784562.77</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>9/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="15" t="n">
+        <v>129971219.82</v>
       </c>
     </row>
   </sheetData>
